--- a/data/trans_orig/P1410-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1410-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2007</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489310</t>
+          <t>489389</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>462494</t>
+          <t>463055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>955198</t>
+          <t>955931</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7770</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>866</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>7694</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>12266</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>727719</t>
+          <t>727867</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>734577</t>
+          <t>734578</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>618094</t>
+          <t>617800</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>625494</t>
+          <t>624628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1349471</t>
+          <t>1348716</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1359036</t>
+          <t>1358246</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>16354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18755</t>
+          <t>19094</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>632180</t>
+          <t>632966</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>673359</t>
+          <t>673390</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>684936</t>
+          <t>685502</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1309657</t>
+          <t>1309318</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1322312</t>
+          <t>1322627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9071</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25162</t>
+          <t>25154</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>20951</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18389</t>
+          <t>18303</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39905</t>
+          <t>40195</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>493985</t>
+          <t>493993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>510076</t>
+          <t>509808</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>495036</t>
+          <t>494691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>508681</t>
+          <t>509469</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>994884</t>
+          <t>994594</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1016400</t>
+          <t>1016486</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30429</t>
+          <t>31651</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56045</t>
+          <t>55350</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29368</t>
+          <t>29559</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48137</t>
+          <t>49443</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78475</t>
+          <t>80182</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>330665</t>
+          <t>331360</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>356281</t>
+          <t>355059</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>374618</t>
+          <t>374427</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>391597</t>
+          <t>392050</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>712221</t>
+          <t>710514</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>742559</t>
+          <t>741253</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30405</t>
+          <t>31026</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54250</t>
+          <t>55036</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>21036</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39362</t>
+          <t>41136</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57575</t>
+          <t>56796</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>87618</t>
+          <t>86843</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>238333</t>
+          <t>237547</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262178</t>
+          <t>261557</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>303572</t>
+          <t>301798</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>322856</t>
+          <t>321898</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>547899</t>
+          <t>548674</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>577942</t>
+          <t>578721</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33966</t>
+          <t>34326</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57590</t>
+          <t>58144</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39595</t>
+          <t>39396</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68210</t>
+          <t>66683</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80602</t>
+          <t>81783</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115929</t>
+          <t>117423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>152293</t>
+          <t>151739</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175917</t>
+          <t>175557</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>265698</t>
+          <t>267225</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>294313</t>
+          <t>294512</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>427862</t>
+          <t>426368</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>463189</t>
+          <t>462008</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>130747</t>
+          <t>128507</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>174841</t>
+          <t>175060</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>105804</t>
+          <t>105205</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>151020</t>
+          <t>150696</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>246944</t>
+          <t>244433</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>308669</t>
+          <t>310370</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3101702</t>
+          <t>3101483</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3145796</t>
+          <t>3148036</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3228177</t>
+          <t>3228501</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3273393</t>
+          <t>3273992</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6347072</t>
+          <t>6345371</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6408797</t>
+          <t>6411308</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2012</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10832</t>
+          <t>11689</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>12758</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448363</t>
+          <t>448384</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>419398</t>
+          <t>418541</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428309</t>
+          <t>428294</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>870731</t>
+          <t>871618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>881475</t>
+          <t>881482</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7298</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>972</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9766</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>679789</t>
+          <t>678908</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>603650</t>
+          <t>604469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1287576</t>
+          <t>1287446</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1296318</t>
+          <t>1296370</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,93%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14813</t>
+          <t>13729</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17631</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>9637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25513</t>
+          <t>27804</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667050</t>
+          <t>668134</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678845</t>
+          <t>678894</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>691943</t>
+          <t>690831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>704783</t>
+          <t>704852</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1365924</t>
+          <t>1363633</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1381894</t>
+          <t>1381800</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24858</t>
+          <t>23311</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>12922</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>29859</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>589759</t>
+          <t>591306</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>608266</t>
+          <t>608230</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>602240</t>
+          <t>601342</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>612114</t>
+          <t>612124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1199938</t>
+          <t>1199021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1218605</t>
+          <t>1218267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15223</t>
+          <t>15253</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32966</t>
+          <t>33039</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17525</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36808</t>
+          <t>36955</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36393</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65734</t>
+          <t>63712</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>396463</t>
+          <t>396390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>414206</t>
+          <t>414176</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>410992</t>
+          <t>410845</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>430275</t>
+          <t>431013</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>811495</t>
+          <t>813517</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>840836</t>
+          <t>841009</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22747</t>
+          <t>21723</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43672</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20658</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41301</t>
+          <t>40781</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47898</t>
+          <t>48052</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77066</t>
+          <t>76214</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266114</t>
+          <t>267246</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287039</t>
+          <t>288063</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>312695</t>
+          <t>313215</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>333338</t>
+          <t>333265</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>586716</t>
+          <t>587568</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>615884</t>
+          <t>615730</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42061</t>
+          <t>41961</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69798</t>
+          <t>69808</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57488</t>
+          <t>57299</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89524</t>
+          <t>88314</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>105286</t>
+          <t>107153</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>146377</t>
+          <t>146850</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>180053</t>
+          <t>180043</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>207790</t>
+          <t>207890</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>298272</t>
+          <t>299482</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>330308</t>
+          <t>330497</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>491270</t>
+          <t>490797</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>532361</t>
+          <t>530494</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,2%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111422</t>
+          <t>111254</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>157498</t>
+          <t>153947</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>125454</t>
+          <t>126734</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>173005</t>
+          <t>174749</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>246614</t>
+          <t>248326</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>316933</t>
+          <t>314820</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3269281</t>
+          <t>3272832</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3315357</t>
+          <t>3315525</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3380911</t>
+          <t>3379167</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3428462</t>
+          <t>3427182</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6663761</t>
+          <t>6665874</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6734080</t>
+          <t>6732368</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2016</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>915</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11594</t>
+          <t>11122</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412760</t>
+          <t>411545</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>387942</t>
+          <t>387943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394841</t>
+          <t>394840</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>803624</t>
+          <t>804096</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>813264</t>
+          <t>813302</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,74 +7049,74 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3888</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>982</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8815</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>3888</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>9590</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3888</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>983</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8858</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3888</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>9738</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>588500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>590496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,77 +7162,77 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>559656</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>554729</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>562562</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1150152</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1144450</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1153054</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>559656</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>554686</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>562561</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1150152</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1144302</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1153053</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14730</t>
+          <t>13658</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>662636</t>
+          <t>663140</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>646656</t>
+          <t>647728</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>658412</t>
+          <t>658524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1313821</t>
+          <t>1313125</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1325881</t>
+          <t>1326189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20417</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25367</t>
+          <t>25708</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19124</t>
+          <t>19077</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40943</t>
+          <t>41556</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>625631</t>
+          <t>625133</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639626</t>
+          <t>639633</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>623710</t>
+          <t>623369</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>640467</t>
+          <t>639689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1254182</t>
+          <t>1253569</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1276001</t>
+          <t>1276048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17818</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41394</t>
+          <t>42089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9954</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27045</t>
+          <t>27639</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32807</t>
+          <t>32210</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62599</t>
+          <t>60379</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>436524</t>
+          <t>435829</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>460100</t>
+          <t>459202</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>469804</t>
+          <t>469210</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>486895</t>
+          <t>486736</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>912168</t>
+          <t>914388</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>941960</t>
+          <t>942557</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30661</t>
+          <t>30065</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54327</t>
+          <t>53494</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33316</t>
+          <t>31556</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59950</t>
+          <t>56479</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69585</t>
+          <t>69767</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>104494</t>
+          <t>105532</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280003</t>
+          <t>280836</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>303669</t>
+          <t>304265</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>317812</t>
+          <t>321283</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>344446</t>
+          <t>346206</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>607598</t>
+          <t>606560</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>642507</t>
+          <t>642325</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>30786</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51592</t>
+          <t>52584</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54581</t>
+          <t>52453</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88117</t>
+          <t>88646</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88370</t>
+          <t>91404</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132392</t>
+          <t>132222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>205406</t>
+          <t>204414</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>225788</t>
+          <t>226212</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>312052</t>
+          <t>311523</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>345588</t>
+          <t>347716</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>524775</t>
+          <t>524945</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>568797</t>
+          <t>565763</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>104181</t>
+          <t>105577</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>149380</t>
+          <t>150123</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>133561</t>
+          <t>134252</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>184543</t>
+          <t>187856</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>253079</t>
+          <t>255287</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>320581</t>
+          <t>322397</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3244970</t>
+          <t>3244227</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3290169</t>
+          <t>3288773</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3359999</t>
+          <t>3356686</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3410981</t>
+          <t>3410290</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6618311</t>
+          <t>6616495</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6685813</t>
+          <t>6683605</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2023</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22345</t>
+          <t>26692</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25966</t>
+          <t>24089</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377642</t>
+          <t>373295</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298831</t>
+          <t>299580</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>687221</t>
+          <t>689098</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>9447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>865</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10090</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13957</t>
+          <t>14070</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414295</t>
+          <t>414100</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>501414</t>
+          <t>500923</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510619</t>
+          <t>510639</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>921094</t>
+          <t>920981</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>933326</t>
+          <t>932825</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>13909</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18781</t>
+          <t>17683</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>523350</t>
+          <t>522429</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534205</t>
+          <t>534497</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>533634</t>
+          <t>533868</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540276</t>
+          <t>540346</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1059356</t>
+          <t>1060454</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1073440</t>
+          <t>1073254</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33648</t>
+          <t>33846</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21942</t>
+          <t>21211</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>20302</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49151</t>
+          <t>49376</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>852818</t>
+          <t>852620</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879276</t>
+          <t>877943</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>690556</t>
+          <t>691287</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>703048</t>
+          <t>703121</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1549814</t>
+          <t>1549589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1578588</t>
+          <t>1578663</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36779</t>
+          <t>36362</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62808</t>
+          <t>62802</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12286</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24815</t>
+          <t>25584</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53524</t>
+          <t>52691</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81651</t>
+          <t>81287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>497429</t>
+          <t>497435</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>523458</t>
+          <t>523875</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>519281</t>
+          <t>518512</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>531810</t>
+          <t>532159</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1022682</t>
+          <t>1023046</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1050809</t>
+          <t>1051642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27553</t>
+          <t>27767</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44738</t>
+          <t>45138</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42436</t>
+          <t>41819</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27745</t>
+          <t>28063</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83282</t>
+          <t>83938</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>322709</t>
+          <t>322309</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>339894</t>
+          <t>339680</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>564752</t>
+          <t>565369</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>596868</t>
+          <t>597869</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>891352</t>
+          <t>890696</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>946889</t>
+          <t>946571</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50172</t>
+          <t>49347</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72705</t>
+          <t>73241</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69620</t>
+          <t>69074</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92656</t>
+          <t>92570</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>124735</t>
+          <t>124450</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>155213</t>
+          <t>155052</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>210054</t>
+          <t>209518</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>232587</t>
+          <t>233412</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>332776</t>
+          <t>332862</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>355812</t>
+          <t>356358</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>552978</t>
+          <t>553139</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>583456</t>
+          <t>583741</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>139462</t>
+          <t>132194</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>207281</t>
+          <t>204021</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>121721</t>
+          <t>124331</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>170024</t>
+          <t>172075</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>283106</t>
+          <t>279511</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>361099</t>
+          <t>363416</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3249500</t>
+          <t>3252760</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3317319</t>
+          <t>3324587</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3485694</t>
+          <t>3483643</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3533997</t>
+          <t>3531387</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6751400</t>
+          <t>6749083</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6829393</t>
+          <t>6832988</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1410-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1410-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489389</t>
+          <t>489313</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>463055</t>
+          <t>463085</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>955931</t>
+          <t>954993</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>8503</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>865</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>11354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>727867</t>
+          <t>726986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>734578</t>
+          <t>734572</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>617800</t>
+          <t>617780</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>624628</t>
+          <t>624629</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1348716</t>
+          <t>1349628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1358246</t>
+          <t>1359041</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16354</t>
+          <t>16728</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19094</t>
+          <t>18068</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>632966</t>
+          <t>632238</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>673390</t>
+          <t>673016</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>685502</t>
+          <t>685503</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1309318</t>
+          <t>1310344</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1322627</t>
+          <t>1322649</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25154</t>
+          <t>25846</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,82 +1777,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>12198</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6756</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>20709</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>27565</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>18578</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>39566</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>1,8%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12198</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6173</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20951</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>27565</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>18303</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>40195</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>493993</t>
+          <t>493301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>509808</t>
+          <t>510239</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,82 +1890,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>98,28%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>503444</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>494933</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>508886</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,63%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,98%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1007224</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>995223</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1016211</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>96,18%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>98,2%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>503444</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>494691</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>509469</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,8%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1007224</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>994594</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1016486</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>96,12%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31651</t>
+          <t>31390</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55350</t>
+          <t>55264</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29559</t>
+          <t>30663</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49443</t>
+          <t>48327</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80182</t>
+          <t>76601</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>331360</t>
+          <t>331446</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>355059</t>
+          <t>355320</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>374427</t>
+          <t>373323</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>392050</t>
+          <t>391752</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>710514</t>
+          <t>714095</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>741253</t>
+          <t>742369</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31026</t>
+          <t>31491</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55036</t>
+          <t>54502</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21036</t>
+          <t>20806</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41136</t>
+          <t>40066</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56796</t>
+          <t>55602</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86843</t>
+          <t>86839</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237547</t>
+          <t>238081</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261557</t>
+          <t>261092</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>301798</t>
+          <t>302868</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>321898</t>
+          <t>322128</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>548674</t>
+          <t>548678</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>578721</t>
+          <t>579915</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34326</t>
+          <t>35099</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58144</t>
+          <t>58447</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39396</t>
+          <t>40888</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66683</t>
+          <t>68616</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81783</t>
+          <t>81354</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>117423</t>
+          <t>117923</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>151739</t>
+          <t>151436</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175557</t>
+          <t>174784</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>267225</t>
+          <t>265292</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>294512</t>
+          <t>293020</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>426368</t>
+          <t>425868</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>462008</t>
+          <t>462437</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,04%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>128507</t>
+          <t>128162</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>175060</t>
+          <t>176137</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>105205</t>
+          <t>106550</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>150696</t>
+          <t>149062</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>244433</t>
+          <t>246647</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>310370</t>
+          <t>309740</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3101483</t>
+          <t>3100406</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3148036</t>
+          <t>3148381</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3228501</t>
+          <t>3230135</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3273992</t>
+          <t>3272647</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6345371</t>
+          <t>6346001</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6411308</t>
+          <t>6409094</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12758</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448384</t>
+          <t>447983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>418541</t>
+          <t>418634</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428294</t>
+          <t>428315</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>871618</t>
+          <t>871599</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>881482</t>
+          <t>881502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>678908</t>
+          <t>680847</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>604469</t>
+          <t>603612</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1287446</t>
+          <t>1286941</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1296370</t>
+          <t>1296306</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13729</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18743</t>
+          <t>17763</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>9671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27804</t>
+          <t>27142</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668134</t>
+          <t>668096</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678894</t>
+          <t>678825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>690831</t>
+          <t>691811</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>704852</t>
+          <t>705532</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1363633</t>
+          <t>1364295</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1381800</t>
+          <t>1381766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23311</t>
+          <t>23328</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12922</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29859</t>
+          <t>29334</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>591306</t>
+          <t>591289</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>608230</t>
+          <t>607957</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>601342</t>
+          <t>603223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>612124</t>
+          <t>613144</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1199021</t>
+          <t>1199546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1218267</t>
+          <t>1218479</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>14665</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33039</t>
+          <t>33266</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16787</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36955</t>
+          <t>36429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>36218</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63712</t>
+          <t>63299</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>396390</t>
+          <t>396163</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>414176</t>
+          <t>414764</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>410845</t>
+          <t>411371</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>431013</t>
+          <t>430727</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>813517</t>
+          <t>813930</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>841009</t>
+          <t>841011</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21723</t>
+          <t>21308</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42540</t>
+          <t>42968</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20731</t>
+          <t>19896</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40781</t>
+          <t>41164</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48052</t>
+          <t>47995</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76214</t>
+          <t>76812</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>267246</t>
+          <t>266818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288063</t>
+          <t>288478</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>313215</t>
+          <t>312832</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>333265</t>
+          <t>334100</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>587568</t>
+          <t>586970</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>615730</t>
+          <t>615787</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41961</t>
+          <t>41214</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69808</t>
+          <t>69806</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57299</t>
+          <t>57047</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88314</t>
+          <t>88731</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>107153</t>
+          <t>106976</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>146850</t>
+          <t>150268</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>180043</t>
+          <t>180045</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>207890</t>
+          <t>208637</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>299482</t>
+          <t>299065</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>330497</t>
+          <t>330749</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>490797</t>
+          <t>487379</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>530494</t>
+          <t>530671</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111254</t>
+          <t>111168</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>153947</t>
+          <t>157690</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>126734</t>
+          <t>125933</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>174749</t>
+          <t>174392</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>248326</t>
+          <t>250073</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>314820</t>
+          <t>315456</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3272832</t>
+          <t>3269089</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3315525</t>
+          <t>3315611</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3379167</t>
+          <t>3379524</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3427182</t>
+          <t>3427983</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6665874</t>
+          <t>6665238</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6732368</t>
+          <t>6730621</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>11363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411545</t>
+          <t>411417</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>387943</t>
+          <t>387827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394840</t>
+          <t>394832</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>804096</t>
+          <t>803855</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>813302</t>
+          <t>813289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7069,47 +7069,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9689</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>3888</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>982</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8815</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3888</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>986</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>8843</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>554729</t>
+          <t>553855</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562562</t>
+          <t>562564</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1144450</t>
+          <t>1145197</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1153054</t>
+          <t>1153058</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13658</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>17180</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>663140</t>
+          <t>662397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>647728</t>
+          <t>646921</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>658524</t>
+          <t>658087</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1313125</t>
+          <t>1313303</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1326189</t>
+          <t>1326181</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20915</t>
+          <t>20857</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25708</t>
+          <t>24978</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19077</t>
+          <t>19627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41556</t>
+          <t>41706</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>625133</t>
+          <t>625191</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639633</t>
+          <t>639601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>623369</t>
+          <t>624099</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>639689</t>
+          <t>640514</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1253569</t>
+          <t>1253419</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1276048</t>
+          <t>1275498</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>19528</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42089</t>
+          <t>42257</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27639</t>
+          <t>27010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32210</t>
+          <t>32784</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60379</t>
+          <t>60559</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>435829</t>
+          <t>435661</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>459202</t>
+          <t>458390</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>469210</t>
+          <t>469839</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>486736</t>
+          <t>486765</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>914388</t>
+          <t>914208</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>942557</t>
+          <t>941983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30065</t>
+          <t>30073</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53494</t>
+          <t>53874</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31556</t>
+          <t>32484</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56479</t>
+          <t>58601</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69767</t>
+          <t>68732</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105532</t>
+          <t>101586</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280836</t>
+          <t>280456</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>304265</t>
+          <t>304257</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>321283</t>
+          <t>319161</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>346206</t>
+          <t>345278</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>606560</t>
+          <t>610506</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>642325</t>
+          <t>643360</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,35%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30786</t>
+          <t>31183</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52584</t>
+          <t>51969</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52453</t>
+          <t>54345</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88646</t>
+          <t>88489</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91404</t>
+          <t>92053</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132222</t>
+          <t>132481</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>204414</t>
+          <t>205029</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>226212</t>
+          <t>225815</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>311523</t>
+          <t>311680</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>347716</t>
+          <t>345824</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>524945</t>
+          <t>524686</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>565763</t>
+          <t>565114</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,99%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>105577</t>
+          <t>106988</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>150123</t>
+          <t>151519</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>134252</t>
+          <t>134684</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>187856</t>
+          <t>187085</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>255287</t>
+          <t>255624</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>322397</t>
+          <t>324470</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3244227</t>
+          <t>3242831</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3288773</t>
+          <t>3287362</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3356686</t>
+          <t>3357457</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3410290</t>
+          <t>3409858</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6616495</t>
+          <t>6614422</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6683605</t>
+          <t>6683268</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26692</t>
+          <t>21296</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24089</t>
+          <t>21259</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>395632</t>
+          <t>404189</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>373295</t>
+          <t>386497</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,17 +9813,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>310523</t>
+          <t>359431</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>299580</t>
+          <t>347082</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,27 +9848,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>706156</t>
+          <t>763620</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>689098</t>
+          <t>749046</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10018,12 +10018,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>8317</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,22 +10043,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>847</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -10121,27 +10121,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>420874</t>
+          <t>474284</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414100</t>
+          <t>468573</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,27 +10156,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>508138</t>
+          <t>498269</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500923</t>
+          <t>493281</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510639</t>
+          <t>500236</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>929012</t>
+          <t>972553</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>920981</t>
+          <t>965193</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>932825</t>
+          <t>976207</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13909</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7931</t>
+          <t>10133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9610</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>530460</t>
+          <t>614844</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522429</t>
+          <t>606747</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534497</t>
+          <t>618680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>538067</t>
+          <t>616491</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>533868</t>
+          <t>611355</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540346</t>
+          <t>619317</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1068527</t>
+          <t>1231335</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1060454</t>
+          <t>1222263</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1073254</t>
+          <t>1236619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8523</t>
+          <t>14311</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33846</t>
+          <t>32788</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21211</t>
+          <t>23920</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>34855</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20302</t>
+          <t>28320</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49376</t>
+          <t>50766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>866042</t>
+          <t>677269</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>852620</t>
+          <t>666449</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>877943</t>
+          <t>684926</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>698067</t>
+          <t>720036</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>691287</t>
+          <t>712575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>703121</t>
+          <t>725208</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1564110</t>
+          <t>1397305</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1549589</t>
+          <t>1384966</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1578663</t>
+          <t>1407412</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886466</t>
+          <t>699237</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886466</t>
+          <t>699237</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886466</t>
+          <t>699237</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1598965</t>
+          <t>1435732</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1598965</t>
+          <t>1435732</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1598965</t>
+          <t>1435732</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>48539</t>
+          <t>52499</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36362</t>
+          <t>41190</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62802</t>
+          <t>66833</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17510</t>
+          <t>19948</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>13684</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25584</t>
+          <t>28976</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,22 +11107,22 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>66049</t>
+          <t>72447</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52691</t>
+          <t>57936</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81287</t>
+          <t>89324</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>511698</t>
+          <t>555860</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>497435</t>
+          <t>541526</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>523875</t>
+          <t>567169</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>526586</t>
+          <t>586128</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>518512</t>
+          <t>577100</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>532159</t>
+          <t>592392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,22 +11220,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1038284</t>
+          <t>1141988</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1023046</t>
+          <t>1125111</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1051642</t>
+          <t>1156499</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544096</t>
+          <t>606076</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544096</t>
+          <t>606076</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544096</t>
+          <t>606076</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1104333</t>
+          <t>1214435</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1104333</t>
+          <t>1214435</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1104333</t>
+          <t>1214435</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35785</t>
+          <t>37869</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27767</t>
+          <t>29509</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45138</t>
+          <t>46963</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>29065</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41819</t>
+          <t>36522</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>61785</t>
+          <t>66935</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28063</t>
+          <t>56008</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83938</t>
+          <t>80135</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>331662</t>
+          <t>368342</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>322309</t>
+          <t>359248</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>339680</t>
+          <t>376702</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>581188</t>
+          <t>408827</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>565369</t>
+          <t>401370</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>597869</t>
+          <t>416124</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>912849</t>
+          <t>777168</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>890696</t>
+          <t>763968</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>946571</t>
+          <t>788095</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607188</t>
+          <t>437892</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607188</t>
+          <t>437892</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607188</t>
+          <t>437892</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974634</t>
+          <t>844103</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974634</t>
+          <t>844103</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974634</t>
+          <t>844103</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>59306</t>
+          <t>66425</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49347</t>
+          <t>56015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73241</t>
+          <t>79059</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>79879</t>
+          <t>86664</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69074</t>
+          <t>74300</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92570</t>
+          <t>98761</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>139185</t>
+          <t>153089</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>124450</t>
+          <t>134628</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>155052</t>
+          <t>169722</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>223453</t>
+          <t>243773</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>209518</t>
+          <t>231139</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>233412</t>
+          <t>254183</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>345553</t>
+          <t>377544</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>332862</t>
+          <t>365447</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>356358</t>
+          <t>389908</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>569006</t>
+          <t>621318</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>553139</t>
+          <t>604685</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>583741</t>
+          <t>639779</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,62%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425432</t>
+          <t>464208</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425432</t>
+          <t>464208</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425432</t>
+          <t>464208</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708191</t>
+          <t>774407</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708191</t>
+          <t>774407</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708191</t>
+          <t>774407</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>176960</t>
+          <t>190965</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132194</t>
+          <t>166361</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>204021</t>
+          <t>216189</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>147595</t>
+          <t>163028</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>124331</t>
+          <t>143315</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>172075</t>
+          <t>183498</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>324555</t>
+          <t>353993</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>279511</t>
+          <t>323764</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>363416</t>
+          <t>388032</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3279821</t>
+          <t>3338561</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3252760</t>
+          <t>3313337</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3324587</t>
+          <t>3363165</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3508123</t>
+          <t>3566726</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3483643</t>
+          <t>3546256</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3531387</t>
+          <t>3586439</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6787944</t>
+          <t>6905287</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6749083</t>
+          <t>6871248</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6832988</t>
+          <t>6935516</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3456781</t>
+          <t>3529526</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3456781</t>
+          <t>3529526</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3456781</t>
+          <t>3529526</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3655718</t>
+          <t>3729754</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3655718</t>
+          <t>3729754</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3655718</t>
+          <t>3729754</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7112499</t>
+          <t>7259280</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7112499</t>
+          <t>7259280</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7112499</t>
+          <t>7259280</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
